--- a/Reporte_Oportunidades_InmoData.xlsx
+++ b/Reporte_Oportunidades_InmoData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,88 +453,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Villa del Parque, Capital Federal</t>
+          <t>Botánico, Palermo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$ 750.000</t>
+          <t>$ 1.500</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>51 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>104 m² tot.4 amb.3 dorm.1 baño</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-hermoso-2-amb-con-patio-con-amenities-58548744.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-de-departamento-4-ambientes-58540876.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Almagro Norte, Almagro</t>
+          <t>Constitución, Capital Federal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 250.000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40 m² tot.1 amb.1 baño</t>
+          <t>23 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-luminoso-mono-con-amenities-56766015.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-de-estudios-apto-vivienda-o-uso-profesional-54700534.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Villa Pueyrredón, Capital Federal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>USD 800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>65 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
+          <t>90 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-alquila-hermoso-departamento.-58548141.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-3-amb-2-banos.-amoblado.-vista-panoramica-58716582.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colegiales, Capital Federal</t>
+          <t>Almagro Norte, Almagro</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USD 500</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37 m² tot.1 amb.1 baño</t>
+          <t>45 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-virrey-loreto-al-3500-58538389.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-monoambiente-con-gran-balcon!-58616142.html</t>
         </is>
       </c>
     </row>
@@ -546,259 +546,259 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$ 710.000</t>
+          <t>USD 1.100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>95 m² tot.4 amb.3 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-.-reciclado-a-nuevo-53477913.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-v-del-pino-al-2600-seguridad-24hs-55741994.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Belgrano R, Belgrano</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USD 1.350</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>70 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-espectacular-2-ambientes-con-full-amenitites.-duenio-58547715.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa--universitario-busco-inquilino-responsable-ingreso-58716044.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retiro, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USD 1.000</t>
+          <t>$ 450</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>110 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
+          <t>68 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-luminoso-semipiso-en-retiro-58547800.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-dos-ambientes-58715879.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Flores Norte, Flores</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>$ 450.000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>80 m² tot.4 amb.3 dorm.2 baños</t>
+          <t>68 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-piso-alto-58547860.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-58715878.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>La Boca, Capital Federal</t>
+          <t>Palermo, Capital Federal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USD 1.100</t>
+          <t>USD 500</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>60 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>115 m² tot.3 amb.2 dorm.2 baños</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-3-ambientes-amoblado-con-balcon-al-frente-58546654.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-las-canitas-dueno-directo-precio-paquete-todo-incluido-58715857.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>San Nicolás, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$ 900.000</t>
+          <t>$ 670.000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>80 m² tot.4 amb.3 dorm.1 baño1 coch.</t>
+          <t>75 m² tot.3 amb.2 dorm.2 baños2 coch.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-de-estilo-4-amb.-al-frte.-c-bcon.-58547527.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-amoblado-3-ambientes-duena-directa-58715850.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Caballito, Capital Federal</t>
+          <t>Balvanera, Capital Federal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$ 760.000</t>
+          <t>$ 550.000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>44 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>32 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-departamento-refaccionado-en-zona-parque-58547603.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-muy-lindo-monoambiente-al-fte-con-balcon-58715842.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Parque Rivadavia, Caballito</t>
+          <t>Belgrano R, Belgrano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$ 990.000</t>
+          <t>$ 600</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>73 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>65 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-depto.-en-el-corazon-de-caballito-3-amb.-58547443.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-belgrano-58715836.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USD 1.000</t>
+          <t>$ 600</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>40 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>65 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-muy-silencioso-c-vista-panoramica.-58547323.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-recoleta-58715821.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Palermo, Capital Federal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$ 660.000</t>
+          <t>$ 700.000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>70 m² tot.</t>
+          <t>50 m² tot.1 baño</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-58547098.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-con-patio-en-zona-alto-palermo-58715421.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Almagro Norte, Almagro</t>
+          <t>Barrio Norte, Capital Federal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 700.000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>40 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-departamento-de-2-ambientes.-boca-de-subte-50186485.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-con-patio-en-barrio-norte-58715340.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Puerto Madero, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USD 1.500</t>
+          <t>$ 700.000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>68 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-dpto-de-categoria-en-una-de-las-mejores-58547265.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-de-2-ambientes-con-patio-en-58715264.html</t>
         </is>
       </c>
     </row>
@@ -815,41 +815,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>30 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-2-ambientes-y-medio-en-el-centro-callao-linea-d-53331644.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-departamento-58715263.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Palermo Hollywood, Palermo</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USD 2.000</t>
+          <t>$ 550.000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>81 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
+          <t>70 m² tot.1 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-mayo-libre-dueno-directo-luminoso-3-amb-mira-a-amplio-57352245.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa--zona-universitaria-recoleta-departamento-amoblado-58706430.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Belgrano C, Belgrano</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -859,188 +859,100 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>70 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>75 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-dia-ambientes-disponible-belgrano-r-58547152.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-dos-ambientes-58714945.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Palermo Soho, Palermo</t>
+          <t>Parque Chacabuco, Capital Federal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$ 620.000</t>
+          <t>USD 750</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>36 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>45 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-2-ambientes-con-aire-palermo-soho-58105883.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-loft-complejo-full-amenities-en-parque-58714790.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Parque Chas, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$ 670.000</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>43 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>75 m² tot.2 amb.1 dorm.2 baños1 coch.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-amb.-parque-chas-cercano-a-subte-58545731.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-duenos-directo-58714927.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Parque Patricios, Capital Federal</t>
+          <t>Caballito Norte, Caballito</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$ 800.000</t>
+          <t>$ 550.000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>51 m² tot.1 amb.1 dorm.1 baño1 coch.</t>
+          <t>32 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-dzain-patricios-luminoso-58546648.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila.-av-acoyte-y-aranguren-excelente-58714841.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Villa Crespo, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>$ 750.000</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>38 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>75 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-hermoso-dos-ambientes-sin-muebles-58546487.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Recoleta, Capital Federal</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>$ 550</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>70 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-duena-directa-recoleta-58546640.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Recoleta, Capital Federal</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>$ 550.000</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>70 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-equipado-recoleta-58546508.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Botánico, Palermo</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>$ 950.000</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>47 m² tot.2 amb.1 dorm.1 baño</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-depto-2-ambientes-apto-profesional.-58473941.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Palermo Hollywood, Palermo</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>$ 670.000</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>53 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-5to-piso-2-amb-duena-directa-amoblado-58546048.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-duenos-directo-58714878.html</t>
         </is>
       </c>
     </row>
